--- a/templates/TATA Capital/TATA_Collection_Agency_Template_2026-27.xlsx
+++ b/templates/TATA Capital/TATA_Collection_Agency_Template_2026-27.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachit Goyal\Downloads\audit-automation-final\templates\TATA Capital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD3E203-2AFA-4EEE-AED9-A383A0E32CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F10457-1C19-4B94-8E02-9F0AE90E0E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="2652" windowWidth="13152" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="2" r:id="rId1"/>
@@ -724,7 +724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -822,21 +822,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="15" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -845,6 +833,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1164,7 +1155,7 @@
   <dimension ref="A1:J62"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.6640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.6640625" style="36" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.44140625" style="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.44140625" style="25" customWidth="1"/>
@@ -1172,8 +1163,8 @@
     <col min="6" max="6" width="18.5546875" style="25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.5546875" style="25" customWidth="1"/>
     <col min="8" max="8" width="33.6640625" style="25" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="41" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="37" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.6640625" style="25"/>
   </cols>
   <sheetData>
@@ -1255,7 +1246,7 @@
       <c r="I7" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="35" t="s">
         <v>149</v>
       </c>
     </row>
@@ -1321,10 +1312,10 @@
         <f>IF(F10="Yes",5,"0")</f>
         <v>0</v>
       </c>
-      <c r="F10" s="35"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="38"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="27"/>
       <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -1344,10 +1335,10 @@
         <f>IF(F11="Yes",4,"0")</f>
         <v>0</v>
       </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="38"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -1367,10 +1358,10 @@
         <f>IF(F12="Yes",3,"0")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="38"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="27"/>
       <c r="J12" s="39"/>
     </row>
     <row r="13" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -1390,10 +1381,10 @@
         <f>IF(F13="Yes",2,"0")</f>
         <v>0</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="38"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="27"/>
       <c r="J13" s="39"/>
     </row>
     <row r="14" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -1436,10 +1427,10 @@
         <f>IF(F15="Yes",2,"0")</f>
         <v>0</v>
       </c>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="38"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="27"/>
       <c r="J15" s="39"/>
     </row>
     <row r="16" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2031,10 +2022,10 @@
         <f>IF(F41="Yes",2,"0")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="35"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="38"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="27"/>
       <c r="J41" s="39"/>
     </row>
     <row r="42" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2054,10 +2045,10 @@
         <f>IF(F42="Yes",2,"0")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="35"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="38"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="27"/>
       <c r="J42" s="39"/>
     </row>
     <row r="43" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2077,10 +2068,10 @@
         <f>IF(F43="Yes",2,"0")</f>
         <v>0</v>
       </c>
-      <c r="F43" s="35"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="38"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="27"/>
       <c r="J43" s="39"/>
     </row>
     <row r="44" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2169,10 +2160,10 @@
         <f>IF(F47="Yes",2,"0")</f>
         <v>0</v>
       </c>
-      <c r="F47" s="35"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="38"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="27"/>
       <c r="J47" s="39"/>
     </row>
     <row r="48" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2215,10 +2206,10 @@
         <f>IF(F49="Yes",1,"0")</f>
         <v>0</v>
       </c>
-      <c r="F49" s="35"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="38"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="27"/>
       <c r="J49" s="39"/>
     </row>
     <row r="50" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2330,10 +2321,10 @@
         <f>IF(F54="Yes",2,"0")</f>
         <v>0</v>
       </c>
-      <c r="F54" s="35"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="38"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="27"/>
       <c r="J54" s="39"/>
     </row>
     <row r="55" spans="1:10" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -2427,13 +2418,13 @@
       <c r="J58" s="27"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B60" s="42"/>
+      <c r="B60" s="38"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B61" s="42"/>
+      <c r="B61" s="38"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B62" s="42"/>
+      <c r="B62" s="38"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0"/>
@@ -2750,13 +2741,13 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="45"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="1" t="str" cm="1">
         <f t="array" ref="F13">_xlfn.IFS(F12&gt;=80%,B16,F12&gt;=70%,B17,F12&gt;=60%,B18,F12&gt;=50%,B19,F12&lt;=49%,B20)</f>
         <v>E</v>
@@ -2885,14 +2876,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2901,7 +2884,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B89E9B38EF334341B754D8F8D6A719DA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fa1e129258e112aee4cf2e89d18a6563">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xmlns:ns4="2bc29a05-2ca3-4765-9547-41c11361a102" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5debfbfacc377353d2d2775bb411679" ns3:_="" ns4:_="">
     <xsd:import namespace="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
@@ -3140,24 +3123,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05142686-EBCF-43E0-A14A-D80EE15D7AEE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{690F940F-5541-43CF-85B5-16E943A4DE36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3165,7 +3139,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC960972-EEAE-4599-9007-3F4FCECAD8D4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3182,4 +3156,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05142686-EBCF-43E0-A14A-D80EE15D7AEE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="0115396f-2e4a-4d2a-ba9c-df4d17cb71a2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="2bc29a05-2ca3-4765-9547-41c11361a102"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>